--- a/outputs/52807.xlsx
+++ b/outputs/52807.xlsx
@@ -731,56 +731,56 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!E$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!E$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!E$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>3000</v>
       </c>
       <c r="F6" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!F$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!F$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!F$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>3000</v>
       </c>
       <c r="G6" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!G$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!G$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!G$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>3000</v>
       </c>
       <c r="H6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!H$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!H$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!H$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!H$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="I6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!I$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!I$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!I$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!I$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="J6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!J$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!J$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!J$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!J$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="K6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!K$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!K$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!K$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!K$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="L6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!L$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!L$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!L$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!L$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="M6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!M$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!M$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!M$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!M$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="N6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!N$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!N$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!N$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!N$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="O6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!O$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!O$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!O$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!O$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="P6" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!P$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!P$5),SUM(E6:G6)/(12-$D$3))</f>
-        <v>1000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!P$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!P$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C6,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>333.333333333333</v>
       </c>
       <c r="Q6" s="1" t="n">
         <f aca="false">SUM(E6:P6)</f>
-        <v>18000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -791,56 +791,56 @@
         <v>5</v>
       </c>
       <c r="E7" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!E$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!E$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!E$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>6000</v>
       </c>
       <c r="F7" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!F$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!F$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!F$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>6000</v>
       </c>
       <c r="G7" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!G$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!G$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!G$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>6000</v>
       </c>
       <c r="H7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!H$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!H$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!H$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!H$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="I7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!I$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!I$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!I$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!I$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="J7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!J$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!J$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!J$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!J$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="K7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!K$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!K$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!K$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!K$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="L7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!L$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!L$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!L$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!L$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="M7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!M$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!M$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!M$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!M$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="N7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!N$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!N$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!N$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!N$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="O7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!O$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!O$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!O$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!O$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="P7" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!P$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!P$5),SUM(E7:G7)/(12-$D$3))</f>
-        <v>2000</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!P$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!P$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C7,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>666.666666666667</v>
       </c>
       <c r="Q7" s="1" t="n">
         <f aca="false">SUM(E7:P7)</f>
-        <v>36000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -851,56 +851,56 @@
         <v>6</v>
       </c>
       <c r="E8" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!E$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!E$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!E$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>7000</v>
       </c>
       <c r="F8" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!F$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!F$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!F$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>7000</v>
       </c>
       <c r="G8" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!G$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!G$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!G$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>7000</v>
       </c>
       <c r="H8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!H$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!H$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!H$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!H$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="I8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!I$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!I$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!I$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!I$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="J8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!J$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!J$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!J$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!J$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="K8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!K$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!K$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!K$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!K$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="L8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!L$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!L$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!L$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!L$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="M8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!M$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!M$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!M$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!M$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="N8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!N$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!N$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!N$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!N$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="O8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!O$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!O$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!O$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!O$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="P8" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!P$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!P$5),SUM(E8:G8)/(12-$D$3))</f>
-        <v>2333.33333333333</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!P$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!P$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C8,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>777.777777777778</v>
       </c>
       <c r="Q8" s="1" t="n">
         <f aca="false">SUM(E8:P8)</f>
-        <v>42000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -911,56 +911,56 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!E$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!E$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!E$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>2000</v>
       </c>
       <c r="F9" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!F$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!F$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!F$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>2000</v>
       </c>
       <c r="G9" s="1" t="n">
-        <f aca="false">SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!G$5)</f>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!G$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!G$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
         <v>2000</v>
       </c>
       <c r="H9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!H$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!H$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!H$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!H$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="I9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!I$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!I$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!I$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!I$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="J9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!J$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!J$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!J$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!J$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="K9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!K$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!K$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!K$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!K$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="L9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!L$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!L$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!L$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!L$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="M9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!M$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!M$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!M$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!M$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="N9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!N$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!N$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!N$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!N$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="O9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!O$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!O$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!O$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!O$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="P9" s="1" t="n">
-        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!P$5)&lt;&gt;0,SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!P$5),SUM(E9:G9)/(12-$D$3))</f>
-        <v>666.666666666667</v>
+        <f aca="false">IF(SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!P$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!P$5),SUMIFS(Data!$C$2:$C$13,Data!$A$2:$A$13,Summary!$C9,Data!$D$2:$D$13,Summary!$E$5)/(12-D$3))</f>
+        <v>222.222222222222</v>
       </c>
       <c r="Q9" s="1" t="n">
         <f aca="false">SUM(E9:P9)</f>
-        <v>12000</v>
+        <v>8000</v>
       </c>
     </row>
   </sheetData>
